--- a/Databases/Database3Clean/Winter Birds '17 Clean.xlsx
+++ b/Databases/Database3Clean/Winter Birds '17 Clean.xlsx
@@ -4894,7 +4894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI42"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4955,250 +4955,10 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>American Oystercatcher</t>
+          <t>Piping Plover</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
-        <is>
-          <t>American Avocet</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Black-bellied Plover</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Dunlin</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Greater Yellowlegs</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Killdeer</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Least Sandpiper</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Lesser Yellowlegs</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Long-billed Curlew</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Long-billed Dowitcher</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Marbled Godwit</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Piping Plover</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Red Knot</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Ruddy Turnstone</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Sanderling</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Semi-palmated Plover</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Semi-palmated Sandpiper</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>Short-billed Dowitcher</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Snowy Plover</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Spotted Sandpiper</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Western Sandpiper</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Whimbrel</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Willet</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Wilson's Plover</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Wilson's Snipe</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Black Skimmer</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>Bonaparte's Gull</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>Brown Booby</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>Brown Pelican</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>Caspian Tern</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>Common Tern</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>Double-crested Cormorant</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>Forster's Tern</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>Franklin's Gull</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>Glaucous Gull</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>Great Black-backed Gull</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>Herring Gull</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>Laughing Gull</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>Lesser Black-backed Gull</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>Ring-billed Gull</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>Royal Tern</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>Sandwich Tern</t>
-        </is>
-      </c>
-      <c r="BB1" t="inlineStr">
-        <is>
-          <t>Vega Gull</t>
-        </is>
-      </c>
-      <c r="BC1" t="inlineStr">
-        <is>
-          <t>White Pelican</t>
-        </is>
-      </c>
-      <c r="BD1" t="inlineStr">
-        <is>
-          <t>Dowitcher sp (unknown)</t>
-        </is>
-      </c>
-      <c r="BE1" t="inlineStr">
-        <is>
-          <t>Sandpiper sp (unknown)</t>
-        </is>
-      </c>
-      <c r="BF1" t="inlineStr">
-        <is>
-          <t>Yellowlegs sp. (unknown)</t>
-        </is>
-      </c>
-      <c r="BG1" t="inlineStr">
-        <is>
-          <t>Gull sp. (unknown)</t>
-        </is>
-      </c>
-      <c r="BH1" t="inlineStr">
-        <is>
-          <t>GRAND TOTAL</t>
-        </is>
-      </c>
-      <c r="BI1" t="inlineStr">
         <is>
           <t>Comments on survey (tide, etc.). (FYI: We are not collecting data on other species.  Feel free to enter your data into eBird)</t>
         </is>
@@ -5251,153 +5011,9 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>15</v>
-      </c>
-      <c r="O2" t="n">
-        <v>37</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
         <v>2</v>
       </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>151</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>39</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>83</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>86</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>474</v>
-      </c>
-      <c r="BI2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -5446,153 +5062,9 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O3" t="n">
-        <v>27</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
         <v>4</v>
       </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>66</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>52</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>245</v>
-      </c>
-      <c r="BI3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>People - 9, Coyote track -2, Armadillo track 2, Boat 1, Raptors observed in the area.</t>
         </is>
@@ -5645,153 +5117,9 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O4" t="n">
-        <v>55</v>
-      </c>
-      <c r="P4" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>8</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
         <v>5</v>
       </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>105</v>
-      </c>
-      <c r="BI4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -5840,153 +5168,9 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>273</v>
-      </c>
-      <c r="P5" t="n">
         <v>2</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2</v>
-      </c>
-      <c r="X5" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>386</v>
-      </c>
-      <c r="BI5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Survey done near low tide, rising. warm, sunny, quiet.</t>
         </is>
@@ -6039,153 +5223,9 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>6</v>
-      </c>
-      <c r="O6" t="n">
-        <v>249</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
         <v>23</v>
       </c>
-      <c r="X6" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>95</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>233</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>680</v>
-      </c>
-      <c r="BI6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Survey done near low tide, rising. warm, sunny, quiet.</t>
         </is>
@@ -6238,153 +5278,9 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>13</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
         <v>1</v>
       </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>93</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>33</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>154</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>117</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>499</v>
-      </c>
-      <c r="BI7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">People  47, Boats 2, Coyote tracks 2, dog tracks 1.  Fog was heavy and low making far observations a challenge. </t>
         </is>
@@ -6436,86 +5332,10 @@
           <t>Overcast, 68F, Wind SE 5mph</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>7</v>
+      </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
-        <v>37</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="n">
-        <v>177</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="n">
-        <v>327</v>
-      </c>
-      <c r="BI8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -6564,105 +5384,9 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>6</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
-        <v>44</v>
-      </c>
-      <c r="O9" t="n">
-        <v>75</v>
-      </c>
-      <c r="P9" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="n">
-        <v>46</v>
-      </c>
-      <c r="W9" t="n">
         <v>8</v>
       </c>
-      <c r="X9" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>167</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="n">
-        <v>175</v>
-      </c>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="n">
-        <v>405</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="n">
-        <v>114</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>153</v>
-      </c>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>69</v>
-      </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="n">
-        <v>1511</v>
-      </c>
-      <c r="BI9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>*Mike Miller (Audubon FL) surveyed solo from 13:00-14:05(ish), combining his observations with main section of survey (group 5 within survey; a group 6 included but is offshore). People:4, Predators: dog tracks 4, opossum 1, raccoon 1, fox (gray?) 1, Also saw: CLRA 1, BEKI 1, other birds recorded elsewhere. 10:06-13:00 is offcial survey with both of us on Alligator Point/Phipps Preserve TNC property that is a CWA.</t>
         </is>
@@ -6715,153 +5439,9 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>23</v>
-      </c>
-      <c r="O10" t="n">
-        <v>148</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
         <v>10</v>
       </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>50</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>155</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>74</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>39</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>54</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>705</v>
-      </c>
-      <c r="BI10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -6910,153 +5490,9 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>14</v>
-      </c>
-      <c r="O11" t="n">
-        <v>20</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
         <v>3</v>
       </c>
-      <c r="X11" t="n">
-        <v>201</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>104</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>141</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>39</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>178</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>66</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>99</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>28</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>1043</v>
-      </c>
-      <c r="BI11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -7105,153 +5541,9 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>5</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
         <v>3</v>
       </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>71</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>99</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>280</v>
-      </c>
-      <c r="BI12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7285,148 +5577,10 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
+      <c r="L13" t="n">
         <v>2</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>182</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2</v>
-      </c>
-      <c r="X13" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>46</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>83</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>31</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>79</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>80+</t>
-        </is>
-      </c>
-      <c r="BF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>923</v>
-      </c>
-      <c r="BI13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Survey ended a little earlier than expected because of a small craft advisory and incoming dense fog.  </t>
         </is>
@@ -7479,153 +5633,9 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>8</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
         <v>2</v>
       </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>142</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>50</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>62</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>52</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>27</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>485</v>
-      </c>
-      <c r="BI14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -7674,153 +5684,9 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
         <v>1</v>
       </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>223</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>207</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>39</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>285</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>865</v>
-      </c>
-      <c r="BI15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -7869,153 +5735,9 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>30</v>
-      </c>
-      <c r="O16" t="n">
-        <v>150</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>50</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>25</v>
-      </c>
-      <c r="W16" t="n">
         <v>15</v>
       </c>
-      <c r="X16" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>200</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>200</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>300</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>1480</v>
-      </c>
-      <c r="BI16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -8064,153 +5786,9 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
         <v>3</v>
       </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>102</v>
-      </c>
-      <c r="BI17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -8261,153 +5839,9 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>64</v>
-      </c>
-      <c r="O18" t="n">
-        <v>137</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
         <v>2</v>
       </c>
-      <c r="X18" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>87</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>278</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>209</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>918</v>
-      </c>
-      <c r="BI18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -8456,153 +5890,9 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
         <v>9</v>
       </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>9</v>
-      </c>
-      <c r="BI19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Sidney was looking specifically for PIPL during this survey</t>
         </is>
@@ -8657,153 +5947,9 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
         <v>10</v>
       </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>10</v>
-      </c>
-      <c r="BI20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Survey done by foot.</t>
         </is>
@@ -8858,153 +6004,9 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>20</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3</v>
-      </c>
-      <c r="O21" t="n">
-        <v>39</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
         <v>4</v>
       </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>45</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>47</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>141</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>120</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>508</v>
-      </c>
-      <c r="BI21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -9053,111 +6055,9 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>29</v>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>100s across entire route</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>3000+ across entire route</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="n">
-        <v>12</v>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="n">
         <v>11</v>
       </c>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100s </t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>100s</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>100s</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>100s</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>100s</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="n">
-        <v>115</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="n">
-        <v>85</v>
-      </c>
-      <c r="AO22" t="inlineStr"/>
-      <c r="AP22" t="inlineStr"/>
-      <c r="AQ22" t="n">
-        <v>35</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>33</v>
-      </c>
-      <c r="AS22" t="inlineStr"/>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AU22" t="inlineStr"/>
-      <c r="AV22" t="inlineStr"/>
-      <c r="AW22" t="n">
-        <v>75</v>
-      </c>
-      <c r="AX22" t="inlineStr"/>
-      <c r="AY22" t="n">
-        <v>25</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA22" t="inlineStr"/>
-      <c r="BB22" t="inlineStr"/>
-      <c r="BC22" t="n">
-        <v>188</v>
-      </c>
-      <c r="BD22" t="inlineStr"/>
-      <c r="BE22" t="inlineStr"/>
-      <c r="BF22" t="inlineStr"/>
-      <c r="BG22" t="inlineStr"/>
-      <c r="BH22" t="n">
-        <v>619</v>
-      </c>
-      <c r="BI22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">In most locations, shorebirds were in densely-massed, mixed-species, concentrations preventing accurate species counts. large flocks in Nassau Sound were continuously flushing and shifting locations across the entire sound preventing accurate tallies. Birds did not concentrate at traditional sites due to neap tide conditions with flocks occupying lower-elevation substrates in marsh habitats. </t>
         </is>
@@ -9210,153 +6110,9 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
         <v>6</v>
       </c>
-      <c r="X23" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>45</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>43</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>238</v>
-      </c>
-      <c r="BI23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -9405,153 +6161,9 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>2</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
         <v>6</v>
       </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>82</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>400</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>45</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>190</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>75</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>858</v>
-      </c>
-      <c r="BI24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>one guy and his unleashed dog camping on island</t>
         </is>
@@ -9604,153 +6216,9 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
         <v>6</v>
       </c>
-      <c r="X25" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>45</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>43</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>238</v>
-      </c>
-      <c r="BI25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -9799,153 +6267,9 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
         <v>6</v>
       </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>82</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>400</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>45</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>190</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>75</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH26" t="n">
-        <v>858</v>
-      </c>
-      <c r="BI26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>one guy and his unleashed dog camping on island</t>
         </is>
@@ -9998,151 +6322,9 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="n">
-        <v>22</v>
-      </c>
-      <c r="O27" t="n">
-        <v>89</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>3</v>
-      </c>
-      <c r="S27" t="n">
-        <v>4</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>18</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>144</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>220</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>84</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>80</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>80</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>870</v>
-      </c>
-      <c r="BI27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -10191,153 +6373,9 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>10</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>21</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
         <v>3</v>
       </c>
-      <c r="X28" t="n">
-        <v>31</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>91</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>134</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>32</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>414</v>
-      </c>
-      <c r="BI28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -10386,153 +6424,9 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>7</v>
-      </c>
-      <c r="O29" t="n">
-        <v>65</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
         <v>2</v>
       </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>30</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>46</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>30</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>89</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>91</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>23</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>98</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH29" t="n">
-        <v>623</v>
-      </c>
-      <c r="BI29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -10581,153 +6475,9 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>7</v>
-      </c>
-      <c r="O30" t="n">
-        <v>30</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>94</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH30" t="n">
-        <v>226</v>
-      </c>
-      <c r="BI30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -10778,153 +6528,9 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>16</v>
-      </c>
-      <c r="O31" t="n">
-        <v>191</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
         <v>21</v>
       </c>
-      <c r="X31" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>36</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>24</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH31" t="n">
-        <v>546</v>
-      </c>
-      <c r="BI31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -10973,153 +6579,9 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>7</v>
-      </c>
-      <c r="O32" t="n">
-        <v>30</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
         <v>1</v>
       </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>94</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH32" t="n">
-        <v>226</v>
-      </c>
-      <c r="BI32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -11168,153 +6630,9 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>10</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>21</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
         <v>3</v>
       </c>
-      <c r="X33" t="n">
-        <v>31</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>91</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>134</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>32</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH33" t="n">
-        <v>414</v>
-      </c>
-      <c r="BI33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -11363,153 +6681,9 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>16</v>
-      </c>
-      <c r="O34" t="n">
-        <v>191</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
         <v>21</v>
       </c>
-      <c r="X34" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>36</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>24</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH34" t="n">
-        <v>546</v>
-      </c>
-      <c r="BI34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -11558,151 +6732,9 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="n">
-        <v>22</v>
-      </c>
-      <c r="O35" t="n">
-        <v>89</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>3</v>
-      </c>
-      <c r="S35" t="n">
-        <v>4</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>18</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>144</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>220</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>84</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>80</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>80</v>
-      </c>
-      <c r="BH35" t="n">
-        <v>870</v>
-      </c>
-      <c r="BI35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -11751,153 +6783,9 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>7</v>
-      </c>
-      <c r="O36" t="n">
-        <v>65</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>1</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
         <v>2</v>
       </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>30</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>46</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>30</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>89</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>91</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>23</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>98</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH36" t="n">
-        <v>623</v>
-      </c>
-      <c r="BI36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -11946,153 +6834,9 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>223</v>
-      </c>
-      <c r="O37" t="n">
-        <v>252</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
         <v>17</v>
       </c>
-      <c r="X37" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>177</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>107</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>70</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>160</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>57</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH37" t="n">
-        <v>1183</v>
-      </c>
-      <c r="BI37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Tide was falling, most birds were observed roosting. PIPL and WIPL were displaying intraspecies territoriality. Only 2 beach-goers present on shoal at opposite end. </t>
         </is>
@@ -12145,145 +6889,9 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>77</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1054</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>72</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
         <v>33</v>
       </c>
-      <c r="X38" t="n">
-        <v>50</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>183</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>437</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>60</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>178</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>301</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>6</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>31</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>114</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>277</v>
-      </c>
-      <c r="BD38" t="inlineStr"/>
-      <c r="BE38" t="inlineStr"/>
-      <c r="BF38" t="inlineStr"/>
-      <c r="BG38" t="inlineStr"/>
-      <c r="BH38" t="n">
-        <v>2922</v>
-      </c>
-      <c r="BI38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Mid-tide rising, flats still exposed at high tide</t>
         </is>
@@ -12335,70 +6943,10 @@
           <t>Partly cloudy, 75F, Wind SSE 7 mph</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="n">
-        <v>2</v>
-      </c>
-      <c r="O39" t="n">
-        <v>13</v>
-      </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="n">
-        <v>1</v>
-      </c>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
-      <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="inlineStr"/>
-      <c r="AE39" t="inlineStr"/>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="inlineStr"/>
-      <c r="AJ39" t="inlineStr"/>
-      <c r="AK39" t="inlineStr"/>
-      <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="inlineStr"/>
-      <c r="AN39" t="inlineStr"/>
-      <c r="AO39" t="inlineStr"/>
-      <c r="AP39" t="inlineStr"/>
-      <c r="AQ39" t="inlineStr"/>
-      <c r="AR39" t="inlineStr"/>
-      <c r="AS39" t="inlineStr"/>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AU39" t="inlineStr"/>
-      <c r="AV39" t="inlineStr"/>
-      <c r="AW39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX39" t="inlineStr"/>
-      <c r="AY39" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ39" t="inlineStr"/>
-      <c r="BA39" t="inlineStr"/>
-      <c r="BB39" t="inlineStr"/>
-      <c r="BC39" t="inlineStr"/>
-      <c r="BD39" t="inlineStr"/>
-      <c r="BE39" t="inlineStr"/>
-      <c r="BF39" t="inlineStr"/>
-      <c r="BG39" t="inlineStr"/>
-      <c r="BH39" t="n">
-        <v>41</v>
-      </c>
-      <c r="BI39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -12447,153 +6995,9 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="O40" t="n">
-        <v>7</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>667</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>59</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>208</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>87</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH40" t="n">
-        <v>1115</v>
-      </c>
-      <c r="BI40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Low Tide</t>
         </is>
@@ -12645,78 +7049,10 @@
           <t>Sunny</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="n">
-        <v>1</v>
-      </c>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA41" t="inlineStr"/>
-      <c r="AB41" t="inlineStr"/>
-      <c r="AC41" t="inlineStr"/>
-      <c r="AD41" t="inlineStr"/>
-      <c r="AE41" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="inlineStr"/>
-      <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="inlineStr"/>
-      <c r="AJ41" t="inlineStr"/>
-      <c r="AK41" t="inlineStr"/>
-      <c r="AL41" t="inlineStr"/>
-      <c r="AM41" t="inlineStr"/>
-      <c r="AN41" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO41" t="inlineStr"/>
-      <c r="AP41" t="inlineStr"/>
-      <c r="AQ41" t="n">
-        <v>82</v>
-      </c>
-      <c r="AR41" t="inlineStr"/>
-      <c r="AS41" t="inlineStr"/>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AU41" t="inlineStr"/>
-      <c r="AV41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA41" t="inlineStr"/>
-      <c r="BB41" t="inlineStr"/>
-      <c r="BC41" t="inlineStr"/>
-      <c r="BD41" t="inlineStr"/>
-      <c r="BE41" t="inlineStr"/>
-      <c r="BF41" t="inlineStr"/>
-      <c r="BG41" t="inlineStr"/>
-      <c r="BH41" t="n">
-        <v>128</v>
-      </c>
-      <c r="BI41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -12773,153 +7109,9 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>6</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>32</v>
-      </c>
-      <c r="O42" t="n">
-        <v>96</v>
-      </c>
-      <c r="P42" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>2</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
         <v>15</v>
       </c>
-      <c r="X42" t="n">
-        <v>103</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>38</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>59</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>101</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>47</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>280</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>10</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>68</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>100</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>323</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>29</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>75</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>29</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH42" t="n">
-        <v>1418</v>
-      </c>
-      <c r="BI42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">conducted during a low tide survey window.  Much of survey conducted from boat, no other human activity observed on islands during the survey.  </t>
         </is>
